--- a/output/04_Aviat_구성방식별_표준BoM_추정.xlsx
+++ b/output/04_Aviat_구성방식별_표준BoM_추정.xlsx
@@ -999,17 +999,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>K9210612</t>
+          <t>K9210611</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>HAX_4GHz WBX 4 CHANNEL SD OPTION</t>
+          <t>HAX_4GHz WBX 4 CHANNEL</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>HAX_4GHz WBX 4 CHANNEL SD OPTION</t>
+          <t>HAX_4GHz WBX 4 CHANNEL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1028,11 +1028,11 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>4500000</v>
+        <v>6750000</v>
       </c>
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n">
-        <v>4410000</v>
+        <v>6615000</v>
       </c>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="2" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>WBX 4채널 표기(확정, HAX_4GHz WBX 4 CHANNEL SD OPTION)</t>
+          <t>WBX 4채널 표기(확정, HAX_4GHz WBX 4 CHANNEL)</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
@@ -1058,17 +1058,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>K9210611</t>
+          <t>K9210612</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>HAX_4GHz WBX 4 CHANNEL</t>
+          <t>HAX_4GHz WBX 4 CHANNEL SD OPTION</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>HAX_4GHz WBX 4 CHANNEL</t>
+          <t>HAX_4GHz WBX 4 CHANNEL SD OPTION</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1087,11 +1087,11 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>6750000</v>
+        <v>4500000</v>
       </c>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n">
-        <v>6615000</v>
+        <v>4410000</v>
       </c>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>WBX 4채널 표기(확정, HAX_4GHz WBX 4 CHANNEL)</t>
+          <t>WBX 4채널 표기(확정, HAX_4GHz WBX 4 CHANNEL SD OPTION)</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>K9204018</t>
+          <t>K9204015</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>HAX_11GHz WBX 4 CHNNEL</t>
+          <t>HAX_8GHz WBX 4 CHNNEL SD OPTION</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>HAX_11GHz WBX 4 CHNNEL</t>
+          <t>HAX_8GHz WBX 4 CHNNEL SD OPTION</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1146,11 +1146,11 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>6750000</v>
+        <v>4500000</v>
       </c>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n">
-        <v>6547500</v>
+        <v>4365000</v>
       </c>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>WBX 4채널 표기(확정, HAX_11GHz WBX 4 CHNNEL)</t>
+          <t>WBX 4채널 표기(확정, HAX_8GHz WBX 4 CHNNEL SD OPTION)</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -1176,17 +1176,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>K9204015</t>
+          <t>K9204014</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>HAX_8GHz WBX 4 CHNNEL SD OPTION</t>
+          <t>HAX_8GHz WBX 4 CHNNEL</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>HAX_8GHz WBX 4 CHNNEL SD OPTION</t>
+          <t>HAX_8GHz WBX 4 CHNNEL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1205,11 +1205,11 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>4500000</v>
+        <v>6750000</v>
       </c>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n">
-        <v>4365000</v>
+        <v>6547500</v>
       </c>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>WBX 4채널 표기(확정, HAX_8GHz WBX 4 CHNNEL SD OPTION)</t>
+          <t>WBX 4채널 표기(확정, HAX_8GHz WBX 4 CHNNEL)</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -1294,17 +1294,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>K9204014</t>
+          <t>K9204018</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>HAX_8GHz WBX 4 CHNNEL</t>
+          <t>HAX_11GHz WBX 4 CHNNEL</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>HAX_8GHz WBX 4 CHNNEL</t>
+          <t>HAX_11GHz WBX 4 CHNNEL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>WBX 4채널 표기(확정, HAX_8GHz WBX 4 CHNNEL)</t>
+          <t>WBX 4채널 표기(확정, HAX_11GHz WBX 4 CHNNEL)</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
@@ -1420,41 +1420,41 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>K9210610</t>
+          <t>K9210623</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>HAX_WTM 4500XT 4GHz</t>
+          <t>FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>HAX_WTM 4500XT 4GHz</t>
+          <t>FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>WTM</t>
+          <t>Waveguide</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.00 ~ 18.00</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>6000000</v>
+        <v>120000</v>
       </c>
       <c r="H9" s="4">
         <f>E9*G9</f>
         <v/>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5880000</v>
+        <v>117600</v>
       </c>
       <c r="J9" s="4">
         <f>E9*I9</f>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-006(품목4/앵커2); EVT-006(품목4/앵커2); EVT-012(품목3/앵커1)</t>
+          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-006(품목2/앵커2); EVT-006(품목2/앵커2); EVT-012(품목18/앵커1)</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
@@ -1554,41 +1554,41 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>K9210623</t>
+          <t>K9210610</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE</t>
+          <t>HAX_WTM 4500XT 4GHz</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE</t>
+          <t>HAX_WTM 4500XT 4GHz</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Waveguide</t>
+          <t>WTM</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1.00 ~ 18.00</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>120000</v>
+        <v>6000000</v>
       </c>
       <c r="H11" s="4">
         <f>E11*G11</f>
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>117600</v>
+        <v>5880000</v>
       </c>
       <c r="J11" s="4">
         <f>E11*I11</f>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-006(품목2/앵커2); EVT-006(품목2/앵커2); EVT-012(품목18/앵커1)</t>
+          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-006(품목4/앵커2); EVT-006(품목4/앵커2); EVT-012(품목3/앵커1)</t>
         </is>
       </c>
       <c r="N11" s="6" t="inlineStr">
@@ -2025,22 +2025,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>K9188145</t>
+          <t>K9204017</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>CTR 8540 1RU Chassis</t>
+          <t>HAX_8GHz WBX 8 CHNNEL SD OPTION</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CTR 8540 1RU Chassis</t>
+          <t>HAX_8GHz WBX 8 CHNNEL SD OPTION</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>IDU/Chassis</t>
+          <t>WBX</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -2054,11 +2054,11 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>3000000</v>
+        <v>4500000</v>
       </c>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n">
-        <v>2940000</v>
+        <v>4365000</v>
       </c>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>세부규격에 '8+0' 명시(확정)</t>
+          <t>WBX 8채널 표기(확정, HAX_8GHz WBX 8 CHNNEL SD OPTION)</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -2084,22 +2084,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>K9204016</t>
+          <t>K9188145</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>HAX_8GHz WBX 8 CHNNEL</t>
+          <t>CTR 8540 1RU Chassis</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>HAX_8GHz WBX 8 CHNNEL</t>
+          <t>CTR 8540 1RU Chassis</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>WBX</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -2113,11 +2113,11 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>12000000</v>
+        <v>3000000</v>
       </c>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n">
-        <v>11640000</v>
+        <v>2940000</v>
       </c>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>WBX 8채널 표기(확정, HAX_8GHz WBX 8 CHNNEL)</t>
+          <t>세부규격에 '8+0' 명시(확정)</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -2143,17 +2143,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>K9204017</t>
+          <t>K9204016</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>HAX_8GHz WBX 8 CHNNEL SD OPTION</t>
+          <t>HAX_8GHz WBX 8 CHNNEL</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>HAX_8GHz WBX 8 CHNNEL SD OPTION</t>
+          <t>HAX_8GHz WBX 8 CHNNEL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2172,11 +2172,11 @@
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4500000</v>
+        <v>12000000</v>
       </c>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n">
-        <v>4365000</v>
+        <v>11640000</v>
       </c>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>WBX 8채널 표기(확정, HAX_8GHz WBX 8 CHNNEL SD OPTION)</t>
+          <t>WBX 8채널 표기(확정, HAX_8GHz WBX 8 CHNNEL)</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr">
@@ -2202,17 +2202,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>K9204021</t>
+          <t>K9204020</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>HAX_11GHz WBX 8 CHNNEL SD OPTION</t>
+          <t>HAX_11GHz WBX 8 CHNNEL</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>HAX_11GHz WBX 8 CHNNEL SD OPTION</t>
+          <t>HAX_11GHz WBX 8 CHNNEL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2231,11 +2231,11 @@
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4500000</v>
+        <v>12000000</v>
       </c>
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n">
-        <v>4365000</v>
+        <v>11640000</v>
       </c>
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>WBX 8채널 표기(확정, HAX_11GHz WBX 8 CHNNEL SD OPTION)</t>
+          <t>WBX 8채널 표기(확정, HAX_11GHz WBX 8 CHNNEL)</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
@@ -2261,17 +2261,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>K9204020</t>
+          <t>K9204021</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>HAX_11GHz WBX 8 CHNNEL</t>
+          <t>HAX_11GHz WBX 8 CHNNEL SD OPTION</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>HAX_11GHz WBX 8 CHNNEL</t>
+          <t>HAX_11GHz WBX 8 CHNNEL SD OPTION</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2290,11 +2290,11 @@
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>12000000</v>
+        <v>4500000</v>
       </c>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n">
-        <v>11640000</v>
+        <v>4365000</v>
       </c>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>WBX 8채널 표기(확정, HAX_11GHz WBX 8 CHNNEL)</t>
+          <t>WBX 8채널 표기(확정, HAX_11GHz WBX 8 CHNNEL SD OPTION)</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
@@ -2454,41 +2454,41 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>K9210610</t>
+          <t>K9210623</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>HAX_WTM 4500XT 4GHz</t>
+          <t>FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>HAX_WTM 4500XT 4GHz</t>
+          <t>FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>WTM</t>
+          <t>Waveguide</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4.00(고정)</t>
+          <t>2.00(고정)</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>6000000</v>
+        <v>120000</v>
       </c>
       <c r="H11" s="4">
         <f>E11*G11</f>
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>5880000</v>
+        <v>117600</v>
       </c>
       <c r="J11" s="4">
         <f>E11*I11</f>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-007(품목8/앵커2); EVT-007(품목8/앵커2)</t>
+          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-007(품목4/앵커2); EVT-007(품목4/앵커2)</t>
         </is>
       </c>
       <c r="N11" s="6" t="inlineStr">
@@ -2588,41 +2588,41 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>K9210623</t>
+          <t>K9210610</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE</t>
+          <t>HAX_WTM 4500XT 4GHz</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE</t>
+          <t>HAX_WTM 4500XT 4GHz</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Waveguide</t>
+          <t>WTM</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2.00(고정)</t>
+          <t>4.00(고정)</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>120000</v>
+        <v>6000000</v>
       </c>
       <c r="H13" s="4">
         <f>E13*G13</f>
         <v/>
       </c>
       <c r="I13" s="4" t="n">
-        <v>117600</v>
+        <v>5880000</v>
       </c>
       <c r="J13" s="4">
         <f>E13*I13</f>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-007(품목4/앵커2); EVT-007(품목4/앵커2)</t>
+          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-007(품목8/앵커2); EVT-007(품목8/앵커2)</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
@@ -3104,7 +3104,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>4+0 - K9210610(HAX_WTM 4500XT 4GHz)</t>
+          <t>4+0 - K9210623(FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3128,7 +3128,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>4+0 - K9210623(FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE)</t>
+          <t>4+0 - K9210610(HAX_WTM 4500XT 4GHz)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>8+0 - K9210610(HAX_WTM 4500XT 4GHz)</t>
+          <t>8+0 - K9210623(FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -3200,7 +3200,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>8+0 - K9210623(FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE)</t>
+          <t>8+0 - K9210610(HAX_WTM 4500XT 4GHz)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">

--- a/output/04_Aviat_구성방식별_표준BoM_추정.xlsx
+++ b/output/04_Aviat_구성방식별_표준BoM_추정.xlsx
@@ -999,17 +999,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>K9210611</t>
+          <t>K9210612</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>HAX_4GHz WBX 4 CHANNEL</t>
+          <t>HAX_4GHz WBX 4 CHANNEL SD OPTION</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>HAX_4GHz WBX 4 CHANNEL</t>
+          <t>HAX_4GHz WBX 4 CHANNEL SD OPTION</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1028,11 +1028,11 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>6750000</v>
+        <v>4500000</v>
       </c>
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n">
-        <v>6615000</v>
+        <v>4410000</v>
       </c>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="2" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>WBX 4채널 표기(확정, HAX_4GHz WBX 4 CHANNEL)</t>
+          <t>WBX 4채널 표기(확정, HAX_4GHz WBX 4 CHANNEL SD OPTION)</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
@@ -1058,17 +1058,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>K9210612</t>
+          <t>K9210611</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>HAX_4GHz WBX 4 CHANNEL SD OPTION</t>
+          <t>HAX_4GHz WBX 4 CHANNEL</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>HAX_4GHz WBX 4 CHANNEL SD OPTION</t>
+          <t>HAX_4GHz WBX 4 CHANNEL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1087,11 +1087,11 @@
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>4500000</v>
+        <v>6750000</v>
       </c>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n">
-        <v>4410000</v>
+        <v>6615000</v>
       </c>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>WBX 4채널 표기(확정, HAX_4GHz WBX 4 CHANNEL SD OPTION)</t>
+          <t>WBX 4채널 표기(확정, HAX_4GHz WBX 4 CHANNEL)</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
@@ -1176,17 +1176,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>K9204014</t>
+          <t>K9204019</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>HAX_8GHz WBX 4 CHNNEL</t>
+          <t>HAX_11GHz WBX 4 CHNNEL SD OPTION</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>HAX_8GHz WBX 4 CHNNEL</t>
+          <t>HAX_11GHz WBX 4 CHNNEL SD OPTION</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1205,11 +1205,11 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>6750000</v>
+        <v>4500000</v>
       </c>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n">
-        <v>6547500</v>
+        <v>4365000</v>
       </c>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>WBX 4채널 표기(확정, HAX_8GHz WBX 4 CHNNEL)</t>
+          <t>WBX 4채널 표기(확정, HAX_11GHz WBX 4 CHNNEL SD OPTION)</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -1235,17 +1235,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>K9204019</t>
+          <t>K9204018</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>HAX_11GHz WBX 4 CHNNEL SD OPTION</t>
+          <t>HAX_11GHz WBX 4 CHNNEL</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>HAX_11GHz WBX 4 CHNNEL SD OPTION</t>
+          <t>HAX_11GHz WBX 4 CHNNEL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>4500000</v>
+        <v>6750000</v>
       </c>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n">
-        <v>4365000</v>
+        <v>6547500</v>
       </c>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>WBX 4채널 표기(확정, HAX_11GHz WBX 4 CHNNEL SD OPTION)</t>
+          <t>WBX 4채널 표기(확정, HAX_11GHz WBX 4 CHNNEL)</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr">
@@ -1294,17 +1294,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>K9204018</t>
+          <t>K9204014</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>HAX_11GHz WBX 4 CHNNEL</t>
+          <t>HAX_8GHz WBX 4 CHNNEL</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>HAX_11GHz WBX 4 CHNNEL</t>
+          <t>HAX_8GHz WBX 4 CHNNEL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>WBX 4채널 표기(확정, HAX_11GHz WBX 4 CHNNEL)</t>
+          <t>WBX 4채널 표기(확정, HAX_8GHz WBX 4 CHNNEL)</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
@@ -1420,17 +1420,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>K9210623</t>
+          <t>K9210624</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE</t>
+          <t>FLEXIBLE LDF4-50A CABLE 4GHz 2000MM N-TYPE MALE</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE</t>
+          <t>FLEXIBLE LDF4-50A CABLE 4GHz 2000MM N-TYPE MALE</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1439,22 +1439,22 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1.00 ~ 18.00</t>
+          <t>10.00 ~ 15.00</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="H9" s="4">
         <f>E9*G9</f>
         <v/>
       </c>
       <c r="I9" s="4" t="n">
-        <v>117600</v>
+        <v>147000</v>
       </c>
       <c r="J9" s="4">
         <f>E9*I9</f>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-006(품목2/앵커2); EVT-006(품목2/앵커2); EVT-012(품목18/앵커1)</t>
+          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-006(품목20/앵커2); EVT-006(품목20/앵커2); EVT-012(품목15/앵커1)</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
@@ -1487,17 +1487,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>K9210624</t>
+          <t>K9210623</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>FLEXIBLE LDF4-50A CABLE 4GHz 2000MM N-TYPE MALE</t>
+          <t>FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>FLEXIBLE LDF4-50A CABLE 4GHz 2000MM N-TYPE MALE</t>
+          <t>FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1506,22 +1506,22 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10.00 ~ 15.00</t>
+          <t>1.00 ~ 18.00</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>150000</v>
+        <v>120000</v>
       </c>
       <c r="H10" s="4">
         <f>E10*G10</f>
         <v/>
       </c>
       <c r="I10" s="4" t="n">
-        <v>147000</v>
+        <v>117600</v>
       </c>
       <c r="J10" s="4">
         <f>E10*I10</f>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-006(품목20/앵커2); EVT-006(품목20/앵커2); EVT-012(품목15/앵커1)</t>
+          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-006(품목2/앵커2); EVT-006(품목2/앵커2); EVT-012(품목18/앵커1)</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
@@ -2084,22 +2084,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>K9188145</t>
+          <t>K9204020</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>CTR 8540 1RU Chassis</t>
+          <t>HAX_11GHz WBX 8 CHNNEL</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CTR 8540 1RU Chassis</t>
+          <t>HAX_11GHz WBX 8 CHNNEL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>IDU/Chassis</t>
+          <t>WBX</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -2113,11 +2113,11 @@
         </is>
       </c>
       <c r="G5" s="4" t="n">
-        <v>3000000</v>
+        <v>12000000</v>
       </c>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n">
-        <v>2940000</v>
+        <v>11640000</v>
       </c>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>세부규격에 '8+0' 명시(확정)</t>
+          <t>WBX 8채널 표기(확정, HAX_11GHz WBX 8 CHNNEL)</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
@@ -2143,22 +2143,22 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>K9204016</t>
+          <t>K9188145</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>HAX_8GHz WBX 8 CHNNEL</t>
+          <t>CTR 8540 1RU Chassis</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>HAX_8GHz WBX 8 CHNNEL</t>
+          <t>CTR 8540 1RU Chassis</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>WBX</t>
+          <t>IDU/Chassis</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2172,11 +2172,11 @@
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>12000000</v>
+        <v>3000000</v>
       </c>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n">
-        <v>11640000</v>
+        <v>2940000</v>
       </c>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>WBX 8채널 표기(확정, HAX_8GHz WBX 8 CHNNEL)</t>
+          <t>세부규격에 '8+0' 명시(확정)</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr">
@@ -2202,17 +2202,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>K9204020</t>
+          <t>K9204016</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>HAX_11GHz WBX 8 CHNNEL</t>
+          <t>HAX_8GHz WBX 8 CHNNEL</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>HAX_11GHz WBX 8 CHNNEL</t>
+          <t>HAX_8GHz WBX 8 CHNNEL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>WBX 8채널 표기(확정, HAX_11GHz WBX 8 CHNNEL)</t>
+          <t>WBX 8채널 표기(확정, HAX_8GHz WBX 8 CHNNEL)</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
@@ -2320,17 +2320,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>K9210626</t>
+          <t>K9210625</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>PDR48 FIXED CONNECTOR</t>
+          <t>N-TYPE MALE TO PDR48 ADAPTER 4GHz</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>PDR48 FIXED CONNECTOR</t>
+          <t>N-TYPE MALE TO PDR48 ADAPTER 4GHz</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2347,14 +2347,14 @@
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>450000</v>
+        <v>300000</v>
       </c>
       <c r="H9" s="4">
         <f>E9*G9</f>
         <v/>
       </c>
       <c r="I9" s="4" t="n">
-        <v>441000</v>
+        <v>294000</v>
       </c>
       <c r="J9" s="4">
         <f>E9*I9</f>
@@ -2387,41 +2387,41 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>K9210625</t>
+          <t>K9210624</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>N-TYPE MALE TO PDR48 ADAPTER 4GHz</t>
+          <t>FLEXIBLE LDF4-50A CABLE 4GHz 2000MM N-TYPE MALE</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>N-TYPE MALE TO PDR48 ADAPTER 4GHz</t>
+          <t>FLEXIBLE LDF4-50A CABLE 4GHz 2000MM N-TYPE MALE</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Waveguide</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4.00(고정)</t>
+          <t>20.00(고정)</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>300000</v>
+        <v>150000</v>
       </c>
       <c r="H10" s="4">
         <f>E10*G10</f>
         <v/>
       </c>
       <c r="I10" s="4" t="n">
-        <v>294000</v>
+        <v>147000</v>
       </c>
       <c r="J10" s="4">
         <f>E10*I10</f>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-007(품목8/앵커2); EVT-007(품목8/앵커2)</t>
+          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-007(품목40/앵커2); EVT-007(품목40/앵커2)</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
@@ -2521,41 +2521,41 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>K9210624</t>
+          <t>K9210610</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>FLEXIBLE LDF4-50A CABLE 4GHz 2000MM N-TYPE MALE</t>
+          <t>HAX_WTM 4500XT 4GHz</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>FLEXIBLE LDF4-50A CABLE 4GHz 2000MM N-TYPE MALE</t>
+          <t>HAX_WTM 4500XT 4GHz</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Waveguide</t>
+          <t>WTM</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20.00(고정)</t>
+          <t>4.00(고정)</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>150000</v>
+        <v>6000000</v>
       </c>
       <c r="H12" s="4">
         <f>E12*G12</f>
         <v/>
       </c>
       <c r="I12" s="4" t="n">
-        <v>147000</v>
+        <v>5880000</v>
       </c>
       <c r="J12" s="4">
         <f>E12*I12</f>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-007(품목40/앵커2); EVT-007(품목40/앵커2)</t>
+          <t>앵커품목 대비 관측 비율(수량/앵커수량) 기준. 근거 이벤트: EVT-007(품목8/앵커2); EVT-007(품목8/앵커2)</t>
         </is>
       </c>
       <c r="N12" s="6" t="inlineStr">
@@ -2588,22 +2588,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>K9210610</t>
+          <t>K9210626</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>HAX_WTM 4500XT 4GHz</t>
+          <t>PDR48 FIXED CONNECTOR</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>HAX_WTM 4500XT 4GHz</t>
+          <t>PDR48 FIXED CONNECTOR</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>WTM</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
@@ -2615,14 +2615,14 @@
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6000000</v>
+        <v>450000</v>
       </c>
       <c r="H13" s="4">
         <f>E13*G13</f>
         <v/>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5880000</v>
+        <v>441000</v>
       </c>
       <c r="J13" s="4">
         <f>E13*I13</f>
@@ -3104,7 +3104,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>4+0 - K9210623(FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE)</t>
+          <t>4+0 - K9210624(FLEXIBLE LDF4-50A CABLE 4GHz 2000MM N-TYPE MALE)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3116,7 +3116,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>4+0 - K9210624(FLEXIBLE LDF4-50A CABLE 4GHz 2000MM N-TYPE MALE)</t>
+          <t>4+0 - K9210623(FLEXIBLE LMR 600 CABLE 4GHz 1500MM N-TYPE MALE)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>8+0 - K9210626(PDR48 FIXED CONNECTOR)</t>
+          <t>8+0 - K9210625(N-TYPE MALE TO PDR48 ADAPTER 4GHz)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3164,7 +3164,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>8+0 - K9210625(N-TYPE MALE TO PDR48 ADAPTER 4GHz)</t>
+          <t>8+0 - K9210624(FLEXIBLE LDF4-50A CABLE 4GHz 2000MM N-TYPE MALE)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>8+0 - K9210624(FLEXIBLE LDF4-50A CABLE 4GHz 2000MM N-TYPE MALE)</t>
+          <t>8+0 - K9210610(HAX_WTM 4500XT 4GHz)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3200,7 +3200,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>8+0 - K9210610(HAX_WTM 4500XT 4GHz)</t>
+          <t>8+0 - K9210626(PDR48 FIXED CONNECTOR)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
